--- a/projects/kaps2/fill_out/RS020_国内出荷連絡データ(MQ)_候选.xlsx
+++ b/projects/kaps2/fill_out/RS020_国内出荷連絡データ(MQ)_候选.xlsx
@@ -1698,8 +1698,8 @@
     <col width="25.49" customWidth="1" style="98" min="14" max="14"/>
     <col width="22.11" customWidth="1" style="98" min="15" max="15"/>
     <col width="4.99" customWidth="1" style="98" min="16" max="16"/>
-    <col width="36" customWidth="1" style="99" min="17" max="17"/>
-    <col width="10" customWidth="1" style="99" min="18" max="18"/>
+    <col width="40" customWidth="1" style="99" min="17" max="17"/>
+    <col width="18" customWidth="1" style="99" min="18" max="18"/>
     <col width="60" customWidth="1" style="99" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="S3" s="124" t="inlineStr">
         <is>
-          <t>在历史 4 份映射中出现过「ファイルＩＤ（BFIL）」，但都没有对应到 SAP 表字段。推测为接口控制字段（文件ID/序号/状态码 等），不需映射。</t>
+          <t>业务词典判定：接口文件/报文控制字段，不映射</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="S7" s="124" t="inlineStr">
         <is>
-          <t>历史中没有「出荷連絡枝番」的 SAP 映射记录。可能是本接口新增字段或接口内部控制信息；若确属业务字段，请人工指定对应的 SAP 字段。</t>
+          <t>业务词典判定：接口内部序号/枝番，通常不映射 SAP 表</t>
         </is>
       </c>
     </row>
@@ -2424,19 +2424,19 @@
       </c>
       <c r="L13" s="135" t="n"/>
       <c r="N13" s="152" t="n"/>
-      <c r="Q13" s="124" t="inlineStr">
-        <is>
-          <t>（无历史映射 — 可能为接口内部字段）</t>
-        </is>
-      </c>
-      <c r="R13" s="124" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S13" s="124" t="inlineStr">
-        <is>
-          <t>历史中没有「口数」的 SAP 映射记录。可能是本接口新增字段或接口内部控制信息；若确属业务字段，请人工指定对应的 SAP 字段。</t>
+      <c r="Q13" s="136" t="inlineStr">
+        <is>
+          <t>[推测] LIPS.LFIMG（出荷数量）</t>
+        </is>
+      </c>
+      <c r="R13" s="137" t="inlineStr">
+        <is>
+          <t>★（推测）</t>
+        </is>
+      </c>
+      <c r="S13" s="138" t="inlineStr">
+        <is>
+          <t>历史中无直接映射，基于「业务词典规则命中」推测对应到「出荷数量」（LIPS.LFIMG）。 备选：VBAP.KWMENG（受注数量）。 请人工复核。</t>
         </is>
       </c>
     </row>
@@ -2593,19 +2593,19 @@
         </is>
       </c>
       <c r="L16" s="135" t="n"/>
-      <c r="Q16" s="124" t="inlineStr">
-        <is>
-          <t>（无历史映射 — 可能为接口内部字段）</t>
-        </is>
-      </c>
-      <c r="R16" s="124" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S16" s="124" t="inlineStr">
-        <is>
-          <t>历史中没有「荷札№」的 SAP 映射记录。可能是本接口新增字段或接口内部控制信息；若确属业务字段，请人工指定对应的 SAP 字段。</t>
+      <c r="Q16" s="136" t="inlineStr">
+        <is>
+          <t>[推测] VEKP.EXIDV（外部 HU ID）</t>
+        </is>
+      </c>
+      <c r="R16" s="137" t="inlineStr">
+        <is>
+          <t>★（推测）</t>
+        </is>
+      </c>
+      <c r="S16" s="138" t="inlineStr">
+        <is>
+          <t>历史中无直接映射，基于「业务词典规则命中」推测对应到「外部 HU ID」（VEKP.EXIDV）。 备选：LIPS.AESKD+EAN11（得意先設計変更ステータス+国際商品コード (EAN/UPC)）。 请人工复核。</t>
         </is>
       </c>
     </row>
@@ -2648,19 +2648,19 @@
       <c r="J17" s="154" t="n"/>
       <c r="K17" s="134" t="n"/>
       <c r="L17" s="135" t="n"/>
-      <c r="Q17" s="124" t="inlineStr">
-        <is>
-          <t>（无历史映射 — 可能为接口内部字段）</t>
-        </is>
-      </c>
-      <c r="R17" s="124" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S17" s="124" t="inlineStr">
-        <is>
-          <t>历史中没有「出荷連絡数」的 SAP 映射记录。可能是本接口新增字段或接口内部控制信息；若确属业务字段，请人工指定对应的 SAP 字段。</t>
+      <c r="Q17" s="136" t="inlineStr">
+        <is>
+          <t>[推测] LIPS.LFIMG（出荷数量）</t>
+        </is>
+      </c>
+      <c r="R17" s="137" t="inlineStr">
+        <is>
+          <t>★（推测）</t>
+        </is>
+      </c>
+      <c r="S17" s="138" t="inlineStr">
+        <is>
+          <t>历史中无直接映射，基于「业务词典规则命中」推测对应到「出荷数量」（LIPS.LFIMG）。 备选：LIKP.VBELN（出荷伝票）。 请人工复核。</t>
         </is>
       </c>
     </row>
@@ -2703,19 +2703,19 @@
       <c r="J18" s="154" t="n"/>
       <c r="K18" s="134" t="n"/>
       <c r="L18" s="135" t="n"/>
-      <c r="Q18" s="124" t="inlineStr">
-        <is>
-          <t>（无历史映射 — 可能为接口内部字段）</t>
-        </is>
-      </c>
-      <c r="R18" s="124" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S18" s="124" t="inlineStr">
-        <is>
-          <t>历史中没有「出荷連絡不足数」的 SAP 映射记录。可能是本接口新增字段或接口内部控制信息；若确属业务字段，请人工指定对应的 SAP 字段。</t>
+      <c r="Q18" s="136" t="inlineStr">
+        <is>
+          <t>[推测] LIPS.LFIMG（出荷数量）</t>
+        </is>
+      </c>
+      <c r="R18" s="137" t="inlineStr">
+        <is>
+          <t>★（推测）</t>
+        </is>
+      </c>
+      <c r="S18" s="138" t="inlineStr">
+        <is>
+          <t>历史中无直接映射，基于「业务词典规则命中」推测对应到「出荷数量」（LIPS.LFIMG）。 备选：VBAP.KWMENG（受注数量）。 请人工复核。</t>
         </is>
       </c>
     </row>
@@ -2758,19 +2758,19 @@
       <c r="J19" s="154" t="n"/>
       <c r="K19" s="134" t="n"/>
       <c r="L19" s="135" t="n"/>
-      <c r="Q19" s="124" t="inlineStr">
-        <is>
-          <t>（无历史映射 — 可能为接口内部字段）</t>
-        </is>
-      </c>
-      <c r="R19" s="124" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S19" s="124" t="inlineStr">
-        <is>
-          <t>历史中没有「入出庫形態」的 SAP 映射记录。可能是本接口新增字段或接口内部控制信息；若确属业务字段，请人工指定对应的 SAP 字段。</t>
+      <c r="Q19" s="136" t="inlineStr">
+        <is>
+          <t>[推测] LIKP.LFART（納品タイプ）</t>
+        </is>
+      </c>
+      <c r="R19" s="137" t="inlineStr">
+        <is>
+          <t>★（推测）</t>
+        </is>
+      </c>
+      <c r="S19" s="138" t="inlineStr">
+        <is>
+          <t>历史中无直接映射，基于「业务词典规则命中」推测对应到「納品タイプ」（LIKP.LFART）。 备选：VBAK.AUART（販売伝票タイプ）。 请人工复核。</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="S20" s="124" t="inlineStr">
         <is>
-          <t>历史中没有「入出庫連番」的 SAP 映射记录。可能是本接口新增字段或接口内部控制信息；若确属业务字段，请人工指定对应的 SAP 字段。</t>
+          <t>业务词典判定：接口内部序号/枝番，通常不映射 SAP 表</t>
         </is>
       </c>
     </row>
@@ -2876,19 +2876,19 @@
         </is>
       </c>
       <c r="L21" s="135" t="n"/>
-      <c r="Q21" s="124" t="inlineStr">
-        <is>
-          <t>（无历史映射 — 可能为接口内部字段）</t>
-        </is>
-      </c>
-      <c r="R21" s="124" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S21" s="124" t="inlineStr">
-        <is>
-          <t>在历史 3 份映射中出现过「ケース数（SCAS）」，但都没有对应到 SAP 表字段。推测为接口控制字段（文件ID/序号/状态码 等），不需映射。</t>
+      <c r="Q21" s="136" t="inlineStr">
+        <is>
+          <t>[推测] LIPS.LFIMG（出荷数量）</t>
+        </is>
+      </c>
+      <c r="R21" s="137" t="inlineStr">
+        <is>
+          <t>★（推测）</t>
+        </is>
+      </c>
+      <c r="S21" s="138" t="inlineStr">
+        <is>
+          <t>历史中无直接映射，基于「业务词典规则命中」推测对应到「出荷数量」（LIPS.LFIMG）。 备选：VBAP.KWMENG（受注数量）。 请人工复核。</t>
         </is>
       </c>
     </row>
@@ -2931,19 +2931,19 @@
       <c r="J22" s="154" t="n"/>
       <c r="K22" s="134" t="n"/>
       <c r="L22" s="135" t="n"/>
-      <c r="Q22" s="124" t="inlineStr">
-        <is>
-          <t>（无历史映射 — 可能为接口内部字段）</t>
-        </is>
-      </c>
-      <c r="R22" s="124" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S22" s="124" t="inlineStr">
-        <is>
-          <t>历史中没有「荷集めボックスNo」的 SAP 映射记录。可能是本接口新增字段或接口内部控制信息；若确属业务字段，请人工指定对应的 SAP 字段。</t>
+      <c r="Q22" s="136" t="inlineStr">
+        <is>
+          <t>[推测] VEKP.EXIDV（外部 HU ID）</t>
+        </is>
+      </c>
+      <c r="R22" s="137" t="inlineStr">
+        <is>
+          <t>★（推测）</t>
+        </is>
+      </c>
+      <c r="S22" s="138" t="inlineStr">
+        <is>
+          <t>历史中无直接映射，基于「业务词典规则命中」推测对应到「外部 HU ID」（VEKP.EXIDV）。 请人工复核。</t>
         </is>
       </c>
     </row>
@@ -2990,19 +2990,21 @@
         </is>
       </c>
       <c r="L23" s="135" t="n"/>
-      <c r="Q23" s="124" t="inlineStr">
-        <is>
-          <t>（无历史映射 — 可能为接口内部字段）</t>
-        </is>
-      </c>
-      <c r="R23" s="124" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S23" s="124" t="inlineStr">
-        <is>
-          <t>历史中没有「集約得意先納所」的 SAP 映射记录。可能是本接口新增字段或接口内部控制信息；若确属业务字段，请人工指定对应的 SAP 字段。</t>
+      <c r="Q23" s="136" t="inlineStr">
+        <is>
+          <t>得意先→BESG.KUNNR（得意先） ＋ 納所→LIKP.KUNNR（出荷先）</t>
+        </is>
+      </c>
+      <c r="R23" s="137" t="inlineStr">
+        <is>
+          <t>复合字段</t>
+        </is>
+      </c>
+      <c r="S23" s="138" t="inlineStr">
+        <is>
+          <t>本字段由多个子字段拼接，下列对每个子字段分别给出推荐：
+得意先（0.67）：主要映射是「得意先」（BESG.KUNNR），也有若干映射到「受注先」（VBAK.KUNNR）。请结合业务判断。
+納所（0.50）：历史上存在多种映射方式，「出荷先」（LIKP.KUNNR）与「取引先機能出荷先の得意先コード」（VBPA.KUNNR）频次相近。两个 SAP 字段语义不同，请根据实际业务判断应使用哪一个。</t>
         </is>
       </c>
     </row>
@@ -3108,19 +3110,19 @@
         </is>
       </c>
       <c r="L25" s="135" t="n"/>
-      <c r="Q25" s="124" t="inlineStr">
-        <is>
-          <t>（无历史映射 — 可能为接口内部字段）</t>
-        </is>
-      </c>
-      <c r="R25" s="124" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S25" s="124" t="inlineStr">
-        <is>
-          <t>历史中没有「品番（20桁）」的 SAP 映射记录。可能是本接口新增字段或接口内部控制信息；若确属业务字段，请人工指定对应的 SAP 字段。</t>
+      <c r="Q25" s="136" t="inlineStr">
+        <is>
+          <t>[推测] VBAP.MATNR（品目コード）</t>
+        </is>
+      </c>
+      <c r="R25" s="137" t="inlineStr">
+        <is>
+          <t>★（推测）</t>
+        </is>
+      </c>
+      <c r="S25" s="138" t="inlineStr">
+        <is>
+          <t>历史中无直接映射，基于「字段名含关键词 品番；业务词典规则命中」推测对应到「品目コード」（VBAP.MATNR）。 备选：MARA.MATNR（品目コード）。 请人工复核。</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3172,7 @@
       <c r="L26" s="135" t="n"/>
       <c r="Q26" s="124" t="inlineStr">
         <is>
-          <t>（填充字段，跳过）</t>
+          <t>（填充/占位，跳过映射）</t>
         </is>
       </c>
       <c r="R26" s="124" t="inlineStr">
@@ -3555,7 +3557,7 @@
     <mergeCell ref="K18:L18"/>
     <mergeCell ref="K3:L3"/>
   </mergeCells>
-  <dataValidations count="25">
+  <dataValidations count="24">
     <dataValidation sqref="O8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>$O$2:$O$3</formula1>
       <formula2>0</formula2>
@@ -3595,7 +3597,7 @@
       <formula1>"LIPS.NTGEW+BRGEW（正味重量+総重量）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"（无历史映射 — 可能为接口内部字段）,（手动指定）"</formula1>
+      <formula1>"[推测] LIPS.LFIMG（出荷数量）,[推测] VBAP.KWMENG（受注数量）,[推测] EBAN.MENGE（購買依頼数量）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"VBAP.MATNR（品目コード）,VBRP.MATNR（品目コード）,EBAN.MATNR（品目コード）,（手动指定）"</formula1>
@@ -3604,34 +3606,31 @@
       <formula1>"MAKT.MAKTX（品目テキスト）,VBAP.ARKTX（受注明細のテキスト (短)）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"（无历史映射 — 可能为接口内部字段）,（手动指定）"</formula1>
+      <formula1>"[推测] VEKP.EXIDV（外部 HU ID）,[推测] LIPS.AESKD+EAN11（得意先設計変更ステータス+国際商品コード (EAN/UPC)）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"（无历史映射 — 可能为接口内部字段）,（手动指定）"</formula1>
+      <formula1>"[推测] LIPS.LFIMG（出荷数量）,[推测] LIKP.VBELN（出荷伝票）,[推测] VBAP.KWMENG（受注数量）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"（无历史映射 — 可能为接口内部字段）,（手动指定）"</formula1>
+      <formula1>"[推测] LIPS.LFIMG（出荷数量）,[推测] VBAP.KWMENG（受注数量）,[推测] EBAN.MENGE（購買依頼数量）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"（无历史映射 — 可能为接口内部字段）,（手动指定）"</formula1>
+      <formula1>"[推测] LIKP.LFART（納品タイプ）,[推测] VBAK.AUART（販売伝票タイプ）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"（无历史映射 — 可能为接口内部字段）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"（无历史映射 — 可能为接口内部字段）,（手动指定）"</formula1>
+      <formula1>"[推测] LIPS.LFIMG（出荷数量）,[推测] VBAP.KWMENG（受注数量）,[推测] VEKP.EXIDV（外部荷役単位 ID）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"（无历史映射 — 可能为接口内部字段）,（手动指定）"</formula1>
-    </dataValidation>
-    <dataValidation sqref="Q23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"（无历史映射 — 可能为接口内部字段）,（手动指定）"</formula1>
+      <formula1>"[推测] VEKP.EXIDV（外部 HU ID）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"VBAP.MATNR（品目コード）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"（无历史映射 — 可能为接口内部字段）,（手动指定）"</formula1>
+      <formula1>"[推测] VBAP.MATNR（品目コード）,[推测] MARA.MATNR（品目コード）,[推测] EKPO.MATNR（品目コード）,（手动指定）"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/projects/kaps2/fill_out/RS020_国内出荷連絡データ(MQ)_候选.xlsx
+++ b/projects/kaps2/fill_out/RS020_国内出荷連絡データ(MQ)_候选.xlsx
@@ -2424,19 +2424,19 @@
       </c>
       <c r="L13" s="135" t="n"/>
       <c r="N13" s="152" t="n"/>
-      <c r="Q13" s="136" t="inlineStr">
-        <is>
-          <t>[推测] LIPS.LFIMG（出荷数量）</t>
-        </is>
-      </c>
-      <c r="R13" s="137" t="inlineStr">
-        <is>
-          <t>★（推测）</t>
-        </is>
-      </c>
-      <c r="S13" s="138" t="inlineStr">
-        <is>
-          <t>历史中无直接映射，基于「业务词典规则命中」推测对应到「出荷数量」（LIPS.LFIMG）。 备选：VBAP.KWMENG（受注数量）。 请人工复核。</t>
+      <c r="Q13" s="139" t="inlineStr">
+        <is>
+          <t>[AI推测] LIPS.LFIMG（出荷数量）</t>
+        </is>
+      </c>
+      <c r="R13" s="140" t="inlineStr">
+        <is>
+          <t>★（AI推测）</t>
+        </is>
+      </c>
+      <c r="S13" s="141" t="inlineStr">
+        <is>
+          <t>AI 推测（无历史直接命中，信心 0.82）：推荐「出荷数量」（LIPS.LFIMG）——本接口为出荷連絡（LIKP/LIPS 家族），'口数'为出荷明细单位的件数/数量语义，出荷上下文优先映射到 LIPS.LFIMG（出荷数量）。备选：VBAP.KWMENG（累積受注数量） / LIPS.ANZSN（荷姿数/梱包数）。AI 推断仅作参考，请务必人工复核。</t>
         </is>
       </c>
     </row>
@@ -2595,17 +2595,17 @@
       <c r="L16" s="135" t="n"/>
       <c r="Q16" s="136" t="inlineStr">
         <is>
-          <t>[推测] VEKP.EXIDV（外部 HU ID）</t>
+          <t>[AI推测] VEKP.EXIDV（外部ハンドリングユニット識別番号）</t>
         </is>
       </c>
       <c r="R16" s="137" t="inlineStr">
         <is>
-          <t>★（推测）</t>
+          <t>★（AI推测）</t>
         </is>
       </c>
       <c r="S16" s="138" t="inlineStr">
         <is>
-          <t>历史中无直接映射，基于「业务词典规则命中」推测对应到「外部 HU ID」（VEKP.EXIDV）。 备选：LIPS.AESKD+EAN11（得意先設計変更ステータス+国際商品コード (EAN/UPC)）。 请人工复核。</t>
+          <t>AI 推测（无历史直接命中，信心 0.80）：推荐「外部ハンドリングユニット識別番号」（VEKP.EXIDV）——荷札№（MMDD+PC+連番4桁）は物流上の荷札/ラベル識別子であり、SAP では HU（ハンドリングユニット）の外部ID である VEKP.EXIDV に対応するのが標準。業務辞書ルールおよび包装/荷札パターンと一致。备选：LIPS.AESKD（得意先設計変更ステータス） / VEKP.VENUM（内部ハンドリングユニット番号）。AI 推断仅作参考，请务必人工复核。</t>
         </is>
       </c>
     </row>
@@ -2648,19 +2648,19 @@
       <c r="J17" s="154" t="n"/>
       <c r="K17" s="134" t="n"/>
       <c r="L17" s="135" t="n"/>
-      <c r="Q17" s="136" t="inlineStr">
-        <is>
-          <t>[推测] LIPS.LFIMG（出荷数量）</t>
-        </is>
-      </c>
-      <c r="R17" s="137" t="inlineStr">
-        <is>
-          <t>★（推测）</t>
-        </is>
-      </c>
-      <c r="S17" s="138" t="inlineStr">
-        <is>
-          <t>历史中无直接映射，基于「业务词典规则命中」推测对应到「出荷数量」（LIPS.LFIMG）。 备选：LIKP.VBELN（出荷伝票）。 请人工复核。</t>
+      <c r="Q17" s="139" t="inlineStr">
+        <is>
+          <t>[AI推测] LIPS.LFIMG（出荷数量）</t>
+        </is>
+      </c>
+      <c r="R17" s="140" t="inlineStr">
+        <is>
+          <t>★★（AI推测）</t>
+        </is>
+      </c>
+      <c r="S17" s="141" t="inlineStr">
+        <is>
+          <t>AI 推测（无历史直接命中，信心 0.90）：推荐「出荷数量」（LIPS.LFIMG）——本接口是国内出荷連絡(MQ)入向，LIKP/LIPS 为核心出荷家族；'出荷連絡数' 以'数'结尾 + 出荷明細上下文，业务词典明确指出出荷/交货上下文应选 LIPS.LFIMG。备选：VBAP.KWMENG（累積受注数量） / LIPS.UMVKZ（販売単位への換算係数 (分子)）。AI 推断仅作参考，请务必人工复核。</t>
         </is>
       </c>
     </row>
@@ -2703,19 +2703,19 @@
       <c r="J18" s="154" t="n"/>
       <c r="K18" s="134" t="n"/>
       <c r="L18" s="135" t="n"/>
-      <c r="Q18" s="136" t="inlineStr">
-        <is>
-          <t>[推测] LIPS.LFIMG（出荷数量）</t>
-        </is>
-      </c>
-      <c r="R18" s="137" t="inlineStr">
-        <is>
-          <t>★（推测）</t>
-        </is>
-      </c>
-      <c r="S18" s="138" t="inlineStr">
-        <is>
-          <t>历史中无直接映射，基于「业务词典规则命中」推测对应到「出荷数量」（LIPS.LFIMG）。 备选：VBAP.KWMENG（受注数量）。 请人工复核。</t>
+      <c r="Q18" s="139" t="inlineStr">
+        <is>
+          <t>[AI推测] LIPS.LFIMG（出荷数量 (販売単位)）</t>
+        </is>
+      </c>
+      <c r="R18" s="140" t="inlineStr">
+        <is>
+          <t>★（AI推测）</t>
+        </is>
+      </c>
+      <c r="S18" s="141" t="inlineStr">
+        <is>
+          <t>AI 推测（无历史直接命中，信心 0.72）：推荐「出荷数量 (販売単位)」（LIPS.LFIMG）——本接口为国内出荷連絡(MQ)，LIPS 家族已强命中。'不足数' 表示出荷連絡で通知された不足分の数量，属于出荷明細数量概念，最接近 LIPS.LFIMG（出荷数量）。SAP 标准无专用'不足数'字段，一般以差分数量存入 LIPS 明細数量。。备选：LIPS.LGMNG（出荷数量 (基本単位)） / VBAP.KWMENG（受注数量 (販売単位)）。AI 推断仅作参考，请务必人工复核。</t>
         </is>
       </c>
     </row>
@@ -2760,17 +2760,17 @@
       <c r="L19" s="135" t="n"/>
       <c r="Q19" s="136" t="inlineStr">
         <is>
-          <t>[推测] LIKP.LFART（納品タイプ）</t>
+          <t>[AI推测] LIKP.LFART（納品タイプ）</t>
         </is>
       </c>
       <c r="R19" s="137" t="inlineStr">
         <is>
-          <t>★（推测）</t>
+          <t>★（AI推测）</t>
         </is>
       </c>
       <c r="S19" s="138" t="inlineStr">
         <is>
-          <t>历史中无直接映射，基于「业务词典规则命中」推测对应到「納品タイプ」（LIKP.LFART）。 备选：VBAK.AUART（販売伝票タイプ）。 请人工复核。</t>
+          <t>AI 推测（无历史直接命中，信心 0.82）：推荐「納品タイプ」（LIKP.LFART）——入出庫形態=入出荷の種類/区分。本接口は出荷連絡(LIKP/LIPS)中心で、'形態'は分類キー。出荷伝票ヘッダの納品タイプ LIKP.LFART が最有力。長さ3/C型とも LFART (CHAR4) に近く整合。。备选：VBAK.AUART（販売伝票タイプ） / VBKD.VSART（出荷タイプ）。AI 推断仅作参考，请务必人工复核。</t>
         </is>
       </c>
     </row>
@@ -2876,19 +2876,19 @@
         </is>
       </c>
       <c r="L21" s="135" t="n"/>
-      <c r="Q21" s="136" t="inlineStr">
-        <is>
-          <t>[推测] LIPS.LFIMG（出荷数量）</t>
-        </is>
-      </c>
-      <c r="R21" s="137" t="inlineStr">
-        <is>
-          <t>★（推测）</t>
-        </is>
-      </c>
-      <c r="S21" s="138" t="inlineStr">
-        <is>
-          <t>历史中无直接映射，基于「业务词典规则命中」推测对应到「出荷数量」（LIPS.LFIMG）。 备选：VBAP.KWMENG（受注数量）。 请人工复核。</t>
+      <c r="Q21" s="139" t="inlineStr">
+        <is>
+          <t>[AI推测] LIPS.ANZPK（荷役単位数）</t>
+        </is>
+      </c>
+      <c r="R21" s="140" t="inlineStr">
+        <is>
+          <t>★（AI推测）</t>
+        </is>
+      </c>
+      <c r="S21" s="141" t="inlineStr">
+        <is>
+          <t>AI 推测（无历史直接命中，信心 0.70）：推荐「荷役単位数」（LIPS.ANZPK）——ケース数=箱/ケースの個数。本接口是出荷連絡(LIKP/LIPS)上下文，LIPS.ANZPK 表示出荷明細に紐づく荷役単位(ケース/パッケージ)の数、长度3位(PIC 999)と整合。备选：VEKP.ANZPA（同一荷役単位数） / LIPS.LFIMG（出荷数量）。AI 推断仅作参考，请务必人工复核。</t>
         </is>
       </c>
     </row>
@@ -2933,17 +2933,17 @@
       <c r="L22" s="135" t="n"/>
       <c r="Q22" s="136" t="inlineStr">
         <is>
-          <t>[推测] VEKP.EXIDV（外部 HU ID）</t>
+          <t>[AI推测] VEKP.EXIDV（外部ハンドリングユニット識別）</t>
         </is>
       </c>
       <c r="R22" s="137" t="inlineStr">
         <is>
-          <t>★（推测）</t>
+          <t>AI推测 需复核</t>
         </is>
       </c>
       <c r="S22" s="138" t="inlineStr">
         <is>
-          <t>历史中无直接映射，基于「业务词典规则命中」推测对应到「外部 HU ID」（VEKP.EXIDV）。 请人工复核。</t>
+          <t>AI 推测（无历史直接命中，信心 0.70）：推荐「外部ハンドリングユニット識別」（VEKP.EXIDV）——『荷集めボックスNo』は出荷ピッキング用の箱番号。業務辞書ヒット（BOX/ボックス → HU 関連）＋入向 IF で外部系から来る箱 ID → HU 外部識別 VEKP.EXIDV が第一候補。。备选：VEKP.VENUM（ハンドリングユニット番号（内部）） / VEPO.VENUM（HU 明細のハンドリングユニット番号）。AI 推断仅作参考，请务必人工复核。</t>
         </is>
       </c>
     </row>
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="L25" s="135" t="n"/>
-      <c r="Q25" s="136" t="inlineStr">
-        <is>
-          <t>[推测] VBAP.MATNR（品目コード）</t>
-        </is>
-      </c>
-      <c r="R25" s="137" t="inlineStr">
-        <is>
-          <t>★（推测）</t>
-        </is>
-      </c>
-      <c r="S25" s="138" t="inlineStr">
-        <is>
-          <t>历史中无直接映射，基于「字段名含关键词 品番；业务词典规则命中」推测对应到「品目コード」（VBAP.MATNR）。 备选：MARA.MATNR（品目コード）。 请人工复核。</t>
+      <c r="Q25" s="139" t="inlineStr">
+        <is>
+          <t>[AI推测] VBAP.MATNR（品目コード）</t>
+        </is>
+      </c>
+      <c r="R25" s="140" t="inlineStr">
+        <is>
+          <t>★（AI推测）</t>
+        </is>
+      </c>
+      <c r="S25" s="141" t="inlineStr">
+        <is>
+          <t>AI 推测（无历史直接命中，信心 0.90）：推荐「品目コード」（VBAP.MATNR）——本接口为出荷連絡（入向），业务明細侧品番历史映射 ×6 均指向 VBAP.MATNR；本书已有 品番(BHIN)→VBAP.MATNR、メーカー略号(BMEKRYG)→VBAP.MATNR 的既定分布，20桁品番沿用相同结构。备选：LIPS.MATNR（品目コード） / MARA.MATNR（品目コード）。AI 推断仅作参考，请务必人工复核。</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3597,7 @@
       <formula1>"LIPS.NTGEW+BRGEW（正味重量+総重量）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"[推测] LIPS.LFIMG（出荷数量）,[推测] VBAP.KWMENG（受注数量）,[推测] EBAN.MENGE（購買依頼数量）,（手动指定）"</formula1>
+      <formula1>"[AI推测] LIPS.LFIMG（出荷数量）,[AI推测] VBAP.KWMENG（累積受注数量）,[AI推测] LIPS.ANZSN（荷姿数/梱包数）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"VBAP.MATNR（品目コード）,VBRP.MATNR（品目コード）,EBAN.MATNR（品目コード）,（手动指定）"</formula1>
@@ -3606,31 +3606,31 @@
       <formula1>"MAKT.MAKTX（品目テキスト）,VBAP.ARKTX（受注明細のテキスト (短)）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"[推测] VEKP.EXIDV（外部 HU ID）,[推测] LIPS.AESKD+EAN11（得意先設計変更ステータス+国際商品コード (EAN/UPC)）,（手动指定）"</formula1>
+      <formula1>"[AI推测] VEKP.EXIDV（外部ハンドリングユニット識別番号）,[AI推测] LIPS.AESKD（得意先設計変更ステータス）,[AI推测] VEKP.VENUM（内部ハンドリングユニット番号）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"[推测] LIPS.LFIMG（出荷数量）,[推测] LIKP.VBELN（出荷伝票）,[推测] VBAP.KWMENG（受注数量）,（手动指定）"</formula1>
+      <formula1>"[AI推测] LIPS.LFIMG（出荷数量）,[AI推测] VBAP.KWMENG（累積受注数量）,[AI推测] LIPS.UMVKZ（販売単位への換算係数 (分子)）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"[推测] LIPS.LFIMG（出荷数量）,[推测] VBAP.KWMENG（受注数量）,[推测] EBAN.MENGE（購買依頼数量）,（手动指定）"</formula1>
+      <formula1>"[AI推测] LIPS.LFIMG（出荷数量 (販売単位)）,[AI推测] LIPS.LGMNG（出荷数量 (基本単位)）,[AI推测] VBAP.KWMENG（受注数量 (販売単位)）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"[推测] LIKP.LFART（納品タイプ）,[推测] VBAK.AUART（販売伝票タイプ）,（手动指定）"</formula1>
+      <formula1>"[AI推测] LIKP.LFART（納品タイプ）,[AI推测] VBAK.AUART（販売伝票タイプ）,[AI推测] VBKD.VSART（出荷タイプ）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"（无历史映射 — 可能为接口内部字段）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"[推测] LIPS.LFIMG（出荷数量）,[推测] VBAP.KWMENG（受注数量）,[推测] VEKP.EXIDV（外部荷役単位 ID）,（手动指定）"</formula1>
+      <formula1>"[AI推测] LIPS.ANZPK（荷役単位数）,[AI推测] VEKP.ANZPA（同一荷役単位数）,[AI推测] LIPS.LFIMG（出荷数量）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"[推测] VEKP.EXIDV（外部 HU ID）,（手动指定）"</formula1>
+      <formula1>"[AI推测] VEKP.EXIDV（外部ハンドリングユニット識別）,[AI推测] VEKP.VENUM（ハンドリングユニット番号（内部））,[AI推测] VEPO.VENUM（HU 明細のハンドリングユニット番号）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"VBAP.MATNR（品目コード）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"[推测] VBAP.MATNR（品目コード）,[推测] MARA.MATNR（品目コード）,[推测] EKPO.MATNR（品目コード）,（手动指定）"</formula1>
+      <formula1>"[AI推测] VBAP.MATNR（品目コード）,[AI推测] LIPS.MATNR（品目コード）,[AI推测] MARA.MATNR（品目コード）,（手动指定）"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/projects/kaps2/fill_out/RS020_国内出荷連絡データ(MQ)_候选.xlsx
+++ b/projects/kaps2/fill_out/RS020_国内出荷連絡データ(MQ)_候选.xlsx
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S13" s="124" t="inlineStr">
         <is>
-          <t>业务词典判定：[AI 判断] 口数 为 C(3) 短字符（PIC'999'），根据类型约束：短 C 字段表示的『数』多为 API 侧的件数聚合统计，SAP 出荷/受注数量字段（LIPS.LFIMG、VBAP.KWMENG 等）均为 QUAN(13,3) 精度数值字段，类型不兼容，严禁强塞；且 LIPS 家族中无与『口数（包装件数）』语义对应且为 CHAR(3) 的标准字段。历史命中 LIPS.AESKD+EAN11 是『荷札№・口数』组合字段且 AESKD 已被本接口 運送会社コード 占用，不适用。判为接口内部/统计字段不映射。</t>
+          <t>业务词典判定：[AI 判断] 项目代码 SKUC『口数』为 C(3) PIC'999'，最大值仅 999，且类型为短 CHAR；按类型/长度约束规则，SAP 真正的数量字段（LIPS.LFIMG / VBAP.KWMENG / MENGE）均为 QUAN(13,3) 精度数值，短 C(3) 字段类型不兼容。该字段语义为『出荷连络一件下的包装件数（口数）』，属接口侧 API 聚合的件数统计值（与每明细行的实际出荷数量 LFIMG 不同，LFIMG 已由其他字段承载于 LIPS 明细）。历史知识库中 IFZ9000101 将『荷札№・口数』强映到 LIPS.AESKD+EAN11 属混合堆叠的不规范映射，不应沿用。综合：判为接口内部聚合统计字段，不映射 SAP。</t>
         </is>
       </c>
     </row>
@@ -2593,19 +2593,19 @@
         </is>
       </c>
       <c r="L16" s="135" t="n"/>
-      <c r="Q16" s="136" t="inlineStr">
-        <is>
-          <t>[AI推测] VEKP.EXIDV（外部ハンドリングユニット識別）</t>
-        </is>
-      </c>
-      <c r="R16" s="137" t="inlineStr">
-        <is>
-          <t>AI推测 需复核</t>
-        </is>
-      </c>
-      <c r="S16" s="138" t="inlineStr">
-        <is>
-          <t>AI 推测（无历史直接命中，信心 0.82）：推荐「外部ハンドリングユニット識別」（VEKP.EXIDV）——荷札№（MMDD+PC+連番4桁 共10桁）是外部系统生成的包装/ラベル识别码，对应 HU 管理中的外部 HU ID。VEKP.EXIDV 为 CHAR(20)，长度足以容纳 C(10)，类型兼容；业务词典规则与历史映射均指向 HU 家族表。。备选：LIPS.AESKD（得意先設計変更ステータス） / VEKP.VENUM（内部ハンドリングユニット番号）。AI 推断仅作参考，请务必人工复核。</t>
+      <c r="Q16" s="139" t="inlineStr">
+        <is>
+          <t>[AI推测] LIPS.AESKD+EAN11（得意先設計変更ステータス+国際商品コード (EAN/UPC)）</t>
+        </is>
+      </c>
+      <c r="R16" s="140" t="inlineStr">
+        <is>
+          <t>★（AI推测）</t>
+        </is>
+      </c>
+      <c r="S16" s="141" t="inlineStr">
+        <is>
+          <t>AI 推测（无历史直接命中，信心 0.78）：推荐「得意先設計変更ステータス+国際商品コード (EAN/UPC)」（LIPS.AESKD+EAN11）——知识库中『荷札』关键词命中的稳定历史映射即 LIPS.AESKD+EAN11（拆字段存放荷札+口数）。类型兼容：C(10) 字符型代码（MMDD+PC+連番4桁），AESKD(CHAR6)+EAN11(CHAR18) 合计承载 24 字符，足以放下 10 位荷札编号；本接口已确定的 LIPS 字段（POSNR/AESKD/NTGEW+BRGEW）也证明本書在 LIPS 上下文，复用同 customer 的拆字段惯例可对齐。。备选：VEKP.EXIDV（外部ハンドリングユニット識別） / LIPS.VBELN_EX（外部識別 1）。AI 推断仅作参考，请务必人工复核。</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="S17" s="124" t="inlineStr">
         <is>
-          <t>业务词典判定：[AI 判断] 字段类型为 C(5) 短字符，按约束规则短 C 字段表示的『数』判定为 API 聚合的件数统计（本接口内对『出荷連絡』条数的汇总值），不应映到 SAP 的 QUAN 数量字段（LFIMG/KWMENG/MENGE 精度 13+3，类型不兼容）。同时本接口的真正业务数量已由『重量(SGYU)』承担，SAP 侧 LIKP/LIPS/VBAP 均无与『出荷連絡の件数』对应的标准 CHAR(5) 字段，视为接口内部聚合字段不做映射。</t>
+          <t>业务词典判定：[AI 判断] 本字段类型为 C(5)，长度仅 5 位，且字段名为『出荷連絡数』（出荷連絡 + 数后缀）。结合本接口为 MQ 入向消息（国内出荷連絡データ MQ），且已跳过同类接口控制字段（ファイルＩＤ/出荷連絡枝番/入出庫連番/予備），此字段极可能是 MQ 消息头中表示『本批出荷連絡明細件数』的 API 聚合计数值，属于接口内部控制字段。SAP 中真正的数量字段（LIPS.LFIMG/VBAP.KWMENG）为 QUAN 类型（精度 13+3），与 C(5) 类型不兼容；按类型约束规则『短 C 字段表示的「数」多为 API 聚合的件数统计，应判 skip』，且业务上 SAP 无对应『出荷連絡件数』标准字段，故判定为接口内部字段不需映射。</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="S18" s="124" t="inlineStr">
         <is>
-          <t>业务词典判定：[AI 判断] C(5) 短字符字段。语义为『出荷連絡不足数』（出荷通知的不足件数），属于接口侧的聚合件数统计。SAP 标准数量字段（LIPS.LFIMG、VBAP.KWMENG 等）均为 QUAN(13,3) 高精度数值类型，与 C(5) 类型/精度不兼容；且 SAP 标准表中不存在『出荷連絡明細中不足件数』这一粒度的短 CHAR 标准字段。按规则短 C 字段表示的『数』应判为 API 聚合计数值，不强塞 QUAN 字段。</t>
+          <t>业务词典判定：[AI 判断] C(5) 短字符不兼容 SAP 的 QUAN 数量字段（LIPS.LFIMG/VBAP.KWMENG 等精度为 13+3 的 QUAN）。虽然字段名含『不足数』后缀且业务上是出荷连络场景下的『不足数量』，但 SAP 标准出荷/受注表中并无 C(5) 长度的『不足数』短字段对应——LIPS/VBAP 体系下的差异/不足数量都是 QUAN 型。该字段长度仅 5 位、且备注为空，更像是接口侧对件数/不足明细数的聚合计数（API 内部统计用），不宜强塞到 SAP 的精确数量字段。判为接口内部字段，不映射。</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="S19" s="138" t="inlineStr">
         <is>
-          <t>AI 推测（无历史直接命中，信心 0.78）：推荐「納品タイプ」（LIKP.LFART）——『入出庫形態』是分类/区分型字段，C(3) 短字符与 SAP LFART (CHAR 4) 长度兼容；本接口为出荷連絡（LIKP/LIPS 家族），出荷系の形態/種類通常映到 LIKP.LFART（納品タイプ），业务词典规则也命中此项。备选：VBAK.AUART（販売伝票タイプ） / VBKD.VSART（出荷タイプ）。AI 推断仅作参考，请务必人工复核。</t>
+          <t>AI 推测（无历史直接命中，信心 0.82）：推荐「納品タイプ」（LIKP.LFART）——字段名『入出庫形態』含『形態』关键词，命中业务词典『形態|種類|区分|タイプ』规则；本接口为出荷連絡（LIKP/LIPS 家族，已确定 LIKP.VBELN/WADAT），出荷側分类对应 LIKP.LFART。LFART 为 CHAR(4)，C(3) 完全兼容（短字符代码字段）。。备选：VBAK.AUART（販売伝票タイプ） / LIKP.VBTYP（SD伝票カテゴリ）。AI 推断仅作参考，请务必人工复核。</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="S21" s="124" t="inlineStr">
         <is>
-          <t>业务词典判定：[AI 判断] ケース数 定义为 C(3) PIC'999'，最大值 999，长度精度远低于 SAP QUAN 数量字段（LFIMG/KWMENG/MENGE 精度 13+3），类型不兼容，不应强塞到真正的数量字段。该字段为 API 侧对本出荷连络明细的『箱/ケース件数』聚合计数值，SAP 标准 LIKP/LIPS/VBAP 家族中无对应的短 NUMC(3) 件数字段；VEKP.ANZGE 等荷役单位数量字段也属 QUAN 长精度，不兼容。因此判为接口内部聚合字段，不做映射。</t>
+          <t>业务词典判定：[AI 判断] ケース数 为 C(3) PIC'999' 短字符无符号数（最大值 999），按类型/长度规则判定为接口侧聚合的件数统计：SAP 数量字段（VEPO.VEMNG / LIPS.LFIMG / VBAP.KWMENG 等）均为 QUAN(13,3) 精确数值，类型不兼容，严禁强塞；而 SAP 标准表中并无与『出荷ケース数』直接对应的 NUMC(3) 字段——历史上対向系统（関連メーカ・全農）将『ケース』相关字段都映到 VEKP.EXIDV/VEPO.UNVEL 这类荷役単位 ID（CHAR），从未映到件数计数。本接口 LIKP/LIPS 家族下出荷数量已由 LIPS.LFIMG（重量已由 LIPS.NTGEW+BRGEW）承载，本字段是 MQ 报文层面对明细行 ケース 数的汇总，属接口内部聚合值，不需映射 SAP 字段。</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="S22" s="138" t="inlineStr">
         <is>
-          <t>AI 推测（无历史直接命中，信心 0.78）：推荐「外部ハンドリングユニット識別」（VEKP.EXIDV）——『荷集めボックスNo』为集货箱编号，属于搬送単位(HU)外部识别码。VEKP.EXIDV 为 CHAR(20)，可容纳 C(5) 短编码；本接口已出现 LIPS/LIKP 出荷体系，HU 包装识别与出荷明细天然关联，类型/长度兼容。。备选：VEKP.VHILM（包装材料） / VEPO.VENUM（内部ハンドリングユニット番号）。AI 推断仅作参考，请务必人工复核。</t>
+          <t>AI 推测（无历史直接命中，信心 0.78）：推荐「外部ハンドリングユニット識別」（VEKP.EXIDV）——项目名『荷集めボックスNo』指向搬送単位/HU（BOX 命中业务词典 VEKP/VEPO）；C(5) 短字符与 EXIDV 的 CHAR 型兼容（EXIDV 标准长度 20，可容纳 5 位编码）。出荷連絡(MQ) 入向场景下，外部系统传入的 BOX No 通常以外部 HU ID 形式落到 VEKP.EXIDV。。备选：VEKP.VENUM（内部ハンドリングユニット番号） / LIPS.VEMNG（梱包数量）。AI 推断仅作参考，请务必人工复核。</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="S25" s="141" t="inlineStr">
         <is>
-          <t>AI 推测（无历史直接命中，信心 0.90）：推荐「品目コード」（VBAP.MATNR）——C(20) 与 SAP MATNR（CHAR 18/40）长度兼容；本接口为国内出荷連絡（VBAK/VBAP/LIKP/LIPS 家族），已有 VBAP.POSNR/VBAP.MATNR 等販売伝票明細字段，品番在業務明細中映到 VBAP.MATNR（历史命中 6 次，同字段 BHIN 已在本书映到 VBAP.MATNR）。备选：LIPS.MATNR（品目コード） / MARA.MATNR（品目コード）。AI 推断仅作参考，请务必人工复核。</t>
+          <t>AI 推测（无历史直接命中，信心 0.92）：推荐「品目コード」（VBAP.MATNR）——C(20) 与 SAP MATNR (CHAR 18/40) 长度兼容；本接口为出荷連絡（VBAK/VBAP/LIKP/LIPS 家族），同书已确定『品番(BHIN)→VBAP.MATNR』，知识库历史『品番→VBAP.MATNR×6』高频稳定，业务明細层应映 VBAP.MATNR。备选：MARA.MATNR（品目コード） / MAKT.MATNR（品目コード）。AI 推断仅作参考，请务必人工复核。</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       <formula1>"MAKT.MAKTX（品目テキスト）,VBAP.ARKTX（受注明細のテキスト (短)）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"[AI推测] VEKP.EXIDV（外部ハンドリングユニット識別）,[AI推测] LIPS.AESKD（得意先設計変更ステータス）,[AI推测] VEKP.VENUM（内部ハンドリングユニット番号）,（手动指定）"</formula1>
+      <formula1>"[AI推测] LIPS.AESKD+EAN11（得意先設計変更ステータス+国際商品コード (EAN/UPC)）,[AI推测] VEKP.EXIDV（外部ハンドリングユニット識別）,[AI推测] LIPS.VBELN_EX（外部識別 1）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"（无历史映射 — 可能为接口内部字段）,（手动指定）"</formula1>
@@ -3615,7 +3615,7 @@
       <formula1>"（无历史映射 — 可能为接口内部字段）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"[AI推测] LIKP.LFART（納品タイプ）,[AI推测] VBAK.AUART（販売伝票タイプ）,[AI推测] VBKD.VSART（出荷タイプ）,（手动指定）"</formula1>
+      <formula1>"[AI推测] LIKP.LFART（納品タイプ）,[AI推测] VBAK.AUART（販売伝票タイプ）,[AI推测] LIKP.VBTYP（SD伝票カテゴリ）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"（无历史映射 — 可能为接口内部字段）,（手动指定）"</formula1>
@@ -3624,13 +3624,13 @@
       <formula1>"（无历史映射 — 可能为接口内部字段）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"[AI推测] VEKP.EXIDV（外部ハンドリングユニット識別）,[AI推测] VEKP.VHILM（包装材料）,[AI推测] VEPO.VENUM（内部ハンドリングユニット番号）,（手动指定）"</formula1>
+      <formula1>"[AI推测] VEKP.EXIDV（外部ハンドリングユニット識別）,[AI推测] VEKP.VENUM（内部ハンドリングユニット番号）,[AI推测] LIPS.VEMNG（梱包数量）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"VBAP.MATNR（品目コード）,（手动指定）"</formula1>
     </dataValidation>
     <dataValidation sqref="Q25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"[AI推测] VBAP.MATNR（品目コード）,[AI推测] LIPS.MATNR（品目コード）,[AI推测] MARA.MATNR（品目コード）,（手动指定）"</formula1>
+      <formula1>"[AI推测] VBAP.MATNR（品目コード）,[AI推测] MARA.MATNR（品目コード）,[AI推测] MAKT.MATNR（品目コード）,（手动指定）"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
